--- a/src/test/resources/ExcelTestData/ExcelData.xlsx
+++ b/src/test/resources/ExcelTestData/ExcelData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakhy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakhy\eclipse-workspace-new\DS_algo_project\src\test\resources\ExcelTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCC24FB-5BA7-4532-A038-C5412ACA81B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2B2CF4-5538-48C2-805B-DEE36BAE3C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2990" yWindow="4010" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Logindetails" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Username</t>
   </si>
@@ -31,18 +31,6 @@
   </si>
   <si>
     <t>Expected message</t>
-  </si>
-  <si>
-    <t>Fill out username field alert</t>
-  </si>
-  <si>
-    <t>Test123</t>
-  </si>
-  <si>
-    <t>Fill out password field alert</t>
-  </si>
-  <si>
-    <t>Test1234</t>
   </si>
   <si>
     <t>Numpysedt192</t>
@@ -372,7 +360,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="27.90625" customWidth="1"/>
@@ -390,46 +378,25 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -450,31 +417,31 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -495,12 +462,12 @@
   <sheetData>
     <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelTestData/ExcelData.xlsx
+++ b/src/test/resources/ExcelTestData/ExcelData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakhy\eclipse-workspace-new\DS_algo_project\src\test\resources\ExcelTestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakhy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2B2CF4-5538-48C2-805B-DEE36BAE3C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF0327E-2DDC-46B6-A400-D4A600A0FB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2990" yWindow="4010" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Logindetails" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Username</t>
   </si>
@@ -83,12 +83,28 @@
   <si>
     <t>Result</t>
   </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>Error occurred during submission</t>
+  </si>
+  <si>
+    <t>NameError: name 'test' is not defined on line 1</t>
+  </si>
+  <si>
+    <t>Element Found
+Not Found</t>
+  </si>
+  <si>
+    <t>Submission Successful</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -110,6 +126,25 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -137,11 +172,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -361,12 +406,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="27.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -377,7 +422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -388,7 +433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -410,12 +455,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="38.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -423,12 +468,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1">
       <c r="B2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -436,7 +481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -454,20 +499,53 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="51.26953125" customWidth="1"/>
+    <col min="2" max="2" width="38.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
